--- a/data/trans_orig/IQ21C-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ21C-Estudios-trans_orig.xlsx
@@ -2588,7 +2588,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3150</t>
+          <t>3265</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>60,56%</t>
+          <t>62,76%</t>
         </is>
       </c>
     </row>
@@ -2810,7 +2810,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3497</t>
+          <t>3414</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2825,7 +2825,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>67,23%</t>
+          <t>65,63%</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2827</t>
+          <t>3294</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>54,34%</t>
+          <t>63,33%</t>
         </is>
       </c>
     </row>
@@ -3032,7 +3032,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>2993</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3047,7 +3047,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>57,54%</t>
+          <t>62,11%</t>
         </is>
       </c>
     </row>
@@ -3143,7 +3143,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3250</t>
+          <t>3178</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3158,7 +3158,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>62,48%</t>
+          <t>61,09%</t>
         </is>
       </c>
     </row>
@@ -3365,7 +3365,7 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2493</t>
+          <t>2480</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>47,92%</t>
+          <t>47,67%</t>
         </is>
       </c>
     </row>
@@ -5486,7 +5486,7 @@
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>3315</t>
+          <t>3316</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>50,7%</t>
+          <t>50,71%</t>
         </is>
       </c>
     </row>
@@ -5703,12 +5703,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>650</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>4539</t>
+          <t>4165</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5718,12 +5718,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>69,43%</t>
+          <t>63,71%</t>
         </is>
       </c>
     </row>
@@ -5819,7 +5819,7 @@
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>3355</t>
+          <t>3507</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5834,7 +5834,7 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>51,32%</t>
+          <t>53,64%</t>
         </is>
       </c>
     </row>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>3154</t>
+          <t>2515</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -5945,7 +5945,7 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>48,24%</t>
+          <t>38,47%</t>
         </is>
       </c>
     </row>
@@ -6041,7 +6041,7 @@
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>3210</t>
+          <t>3230</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6056,7 +6056,7 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>49,1%</t>
+          <t>49,4%</t>
         </is>
       </c>
     </row>
@@ -6152,7 +6152,7 @@
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>2950</t>
+          <t>3388</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6167,7 +6167,7 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>45,12%</t>
+          <t>51,82%</t>
         </is>
       </c>
     </row>
@@ -6263,7 +6263,7 @@
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>2650</t>
+          <t>2622</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6278,7 +6278,7 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>40,53%</t>
+          <t>40,1%</t>
         </is>
       </c>
     </row>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2511</t>
+          <t>2500</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8373,7 +8373,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>78,78%</t>
+          <t>78,45%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8393,7 +8393,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>2467</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8408,7 +8408,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>41,76%</t>
+          <t>41,85%</t>
         </is>
       </c>
     </row>
@@ -8802,7 +8802,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2714</t>
+          <t>2616</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8817,7 +8817,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>85,17%</t>
+          <t>82,07%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8837,7 +8837,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3313</t>
+          <t>3916</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8852,7 +8852,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>56,08%</t>
+          <t>66,3%</t>
         </is>
       </c>
     </row>
@@ -8913,7 +8913,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2517</t>
+          <t>2506</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8928,7 +8928,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>78,97%</t>
+          <t>78,62%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8948,7 +8948,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2602</t>
+          <t>2595</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8963,7 +8963,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>44,05%</t>
+          <t>43,93%</t>
         </is>
       </c>
     </row>
@@ -9246,7 +9246,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2572</t>
+          <t>2556</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9261,7 +9261,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>80,71%</t>
+          <t>80,21%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9281,7 +9281,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3366</t>
+          <t>3865</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9296,7 +9296,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>56,98%</t>
+          <t>65,42%</t>
         </is>
       </c>
     </row>
@@ -9392,7 +9392,7 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>3875</t>
+          <t>3417</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -9407,7 +9407,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>65,6%</t>
+          <t>57,85%</t>
         </is>
       </c>
     </row>
@@ -9503,7 +9503,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2822</t>
+          <t>2910</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -9518,7 +9518,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>47,78%</t>
+          <t>49,27%</t>
         </is>
       </c>
     </row>
@@ -11145,7 +11145,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>2692</t>
+          <t>3236</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -11160,7 +11160,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>45,98%</t>
+          <t>55,27%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -11180,7 +11180,7 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>2718</t>
+          <t>2702</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -11195,7 +11195,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,45%</t>
         </is>
       </c>
     </row>
@@ -11256,7 +11256,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2445</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -11271,7 +11271,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>41,77%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -11291,7 +11291,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>2482</t>
+          <t>2468</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -11306,7 +11306,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>25,98%</t>
         </is>
       </c>
     </row>
@@ -11554,7 +11554,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>3009</t>
+          <t>3101</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -11569,7 +11569,7 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>82,59%</t>
+          <t>85,12%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -11589,7 +11589,7 @@
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>2680</t>
+          <t>3297</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -11604,7 +11604,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>45,78%</t>
+          <t>56,3%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -11624,7 +11624,7 @@
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>4370</t>
+          <t>4700</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -11639,7 +11639,7 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>46,01%</t>
+          <t>49,48%</t>
         </is>
       </c>
     </row>
@@ -11695,12 +11695,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>644</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>3949</t>
+          <t>4013</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -11710,12 +11710,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>67,44%</t>
+          <t>68,53%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -11730,12 +11730,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>632</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>4783</t>
+          <t>4705</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -11745,12 +11745,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>50,36%</t>
+          <t>49,53%</t>
         </is>
       </c>
     </row>
@@ -11811,7 +11811,7 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>2622</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -11826,7 +11826,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>44,46%</t>
+          <t>44,79%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -11846,7 +11846,7 @@
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>2732</t>
+          <t>2614</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -11861,7 +11861,7 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>27,52%</t>
         </is>
       </c>
     </row>
@@ -12109,7 +12109,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>2843</t>
+          <t>2836</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -12124,7 +12124,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>78,03%</t>
+          <t>77,86%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -12144,7 +12144,7 @@
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>2624</t>
+          <t>2686</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -12159,7 +12159,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>44,82%</t>
+          <t>45,88%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>3784</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>38,46%</t>
         </is>
       </c>
     </row>
@@ -12220,7 +12220,7 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>2936</t>
+          <t>2943</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -12235,7 +12235,7 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>80,6%</t>
+          <t>80,77%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -12290,7 +12290,7 @@
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>4060</t>
+          <t>4022</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -12305,7 +12305,7 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>42,74%</t>
+          <t>42,35%</t>
         </is>
       </c>
     </row>
@@ -12331,7 +12331,7 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>2570</t>
+          <t>2772</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -12346,7 +12346,7 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>70,53%</t>
+          <t>76,08%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -12366,7 +12366,7 @@
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>2671</t>
+          <t>2669</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -12381,7 +12381,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>45,62%</t>
+          <t>45,58%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -12401,7 +12401,7 @@
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>4163</t>
+          <t>4132</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -12416,7 +12416,7 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>43,83%</t>
+          <t>43,5%</t>
         </is>
       </c>
     </row>
@@ -14531,7 +14531,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3064</t>
+          <t>2923</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -14546,7 +14546,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>70,97%</t>
+          <t>67,71%</t>
         </is>
       </c>
     </row>
@@ -14642,7 +14642,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2684</t>
+          <t>2699</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -14657,7 +14657,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>62,18%</t>
+          <t>62,52%</t>
         </is>
       </c>
     </row>
@@ -14718,7 +14718,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2644</t>
+          <t>2259</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -14733,7 +14733,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>76,49%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -14753,7 +14753,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>2985</t>
+          <t>2893</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -14768,7 +14768,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>69,15%</t>
+          <t>67,01%</t>
         </is>
       </c>
     </row>
@@ -15197,7 +15197,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2754</t>
+          <t>2763</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -15212,7 +15212,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>63,79%</t>
+          <t>64,01%</t>
         </is>
       </c>
     </row>
@@ -15419,7 +15419,7 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2904</t>
+          <t>3051</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -15434,7 +15434,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>67,28%</t>
+          <t>70,68%</t>
         </is>
       </c>
     </row>
@@ -15530,7 +15530,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3005</t>
+          <t>3383</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -15545,7 +15545,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>69,62%</t>
+          <t>78,36%</t>
         </is>
       </c>
     </row>
@@ -16646,7 +16646,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>2494</t>
+          <t>2473</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -16661,7 +16661,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>75,86%</t>
+          <t>75,24%</t>
         </is>
       </c>
     </row>
@@ -16757,7 +16757,7 @@
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>2754</t>
+          <t>2752</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -16772,7 +16772,7 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>83,79%</t>
+          <t>83,72%</t>
         </is>
       </c>
     </row>
@@ -17283,7 +17283,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>3180</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -17298,7 +17298,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>72,36%</t>
+          <t>74,95%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -17318,7 +17318,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>3489</t>
+          <t>4198</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -17333,7 +17333,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>38,04%</t>
+          <t>45,77%</t>
         </is>
       </c>
     </row>
@@ -17359,7 +17359,7 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>3021</t>
+          <t>2989</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -17374,7 +17374,7 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>63,24%</t>
+          <t>62,58%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -17429,7 +17429,7 @@
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>3142</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -17444,7 +17444,7 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>39,83%</t>
         </is>
       </c>
     </row>
@@ -17470,7 +17470,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>2663</t>
+          <t>2607</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -17485,7 +17485,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>55,75%</t>
+          <t>54,57%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -17540,7 +17540,7 @@
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>3226</t>
+          <t>2617</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -17555,7 +17555,7 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>28,54%</t>
         </is>
       </c>
     </row>
@@ -17616,7 +17616,7 @@
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>3018</t>
+          <t>2939</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -17631,7 +17631,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>68,69%</t>
+          <t>66,9%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -17651,7 +17651,7 @@
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>3838</t>
+          <t>3726</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -17666,7 +17666,7 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>41,85%</t>
+          <t>40,63%</t>
         </is>
       </c>
     </row>
@@ -17692,7 +17692,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>3208</t>
+          <t>3195</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -17707,7 +17707,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>67,16%</t>
+          <t>66,87%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -17762,7 +17762,7 @@
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>3628</t>
+          <t>3822</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -17777,7 +17777,7 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>39,56%</t>
+          <t>41,67%</t>
         </is>
       </c>
     </row>
@@ -18025,7 +18025,7 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>2442</t>
+          <t>2517</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -18040,7 +18040,7 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>51,12%</t>
+          <t>52,69%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -18060,7 +18060,7 @@
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>2799</t>
+          <t>2818</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -18075,7 +18075,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>63,7%</t>
+          <t>64,13%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -18095,7 +18095,7 @@
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>3555</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -18110,7 +18110,7 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>38,52%</t>
+          <t>38,76%</t>
         </is>
       </c>
     </row>
@@ -18136,7 +18136,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>2896</t>
+          <t>2632</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -18151,7 +18151,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>60,63%</t>
+          <t>55,09%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -18206,7 +18206,7 @@
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>3327</t>
+          <t>2894</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -18221,7 +18221,7 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>36,27%</t>
+          <t>31,56%</t>
         </is>
       </c>
     </row>
@@ -18247,7 +18247,7 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>3406</t>
+          <t>3446</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -18262,7 +18262,7 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>71,3%</t>
+          <t>72,14%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -18282,7 +18282,7 @@
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>3469</t>
+          <t>3382</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -18297,7 +18297,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>78,95%</t>
+          <t>76,96%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -18312,12 +18312,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>697</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>5419</t>
+          <t>5528</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -18327,12 +18327,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>59,09%</t>
+          <t>60,28%</t>
         </is>
       </c>
     </row>
@@ -18393,7 +18393,7 @@
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>3216</t>
+          <t>3102</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -18408,7 +18408,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>73,19%</t>
+          <t>70,59%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -18428,7 +18428,7 @@
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>3746</t>
+          <t>3845</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -18443,7 +18443,7 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>40,85%</t>
+          <t>41,93%</t>
         </is>
       </c>
     </row>
@@ -24344,7 +24344,7 @@
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>3442</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -24359,7 +24359,7 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>85,74%</t>
+          <t>85,95%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ21C-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ21C-Estudios-trans_orig.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +140,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -646,419 +651,217 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>3,9</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>6,0</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>24,0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1,0</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>3,9</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>6,0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>14,08</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="C4" s="5" t="n">
+        <v>3.903184164387139</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="5" t="inlineStr"/>
+      <c r="H4" s="5" t="inlineStr"/>
+      <c r="I4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" s="5" t="inlineStr"/>
+      <c r="K4" s="5" t="n">
+        <v>3.903184164387139</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>14.08191816875732</v>
+      </c>
+      <c r="N4" s="5" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>2,0; 6,0</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>2,0; 6,0</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>1,0; 24,0</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" s="5" t="inlineStr"/>
+      <c r="E5" s="5" t="inlineStr"/>
+      <c r="F5" s="5" t="inlineStr"/>
+      <c r="G5" s="5" t="inlineStr"/>
+      <c r="H5" s="5" t="inlineStr"/>
+      <c r="I5" s="5" t="inlineStr"/>
+      <c r="J5" s="5" t="inlineStr"/>
+      <c r="K5" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="L5" s="5" t="inlineStr"/>
+      <c r="M5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="D6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="5" t="inlineStr"/>
+      <c r="H6" s="5" t="inlineStr"/>
+      <c r="I6" s="5" t="inlineStr"/>
+      <c r="J6" s="5" t="inlineStr"/>
+      <c r="K6" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="L6" s="5" t="inlineStr"/>
+      <c r="M6" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="N6" s="5" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Secundarios</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>6,76</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>8,26</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>2,66</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>3,0</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>3,4</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0,97</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>15,34</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>3,0</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>5,17</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>4,9</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>6,67</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>3,0</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>4,78; 10,41</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>4,18; 20,06</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0,74; 6,06</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>1,95; 5,41</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,23; 1,74</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>12,0; 18,0</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>3,49; 8,0</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>2,19; 12,18</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>2,52; 12,41</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>3,0; 3,0</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>6.763957257594371</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>8.259650110136423</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>2.662123601700332</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>3.398623865093191</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>0.9673887467928539</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>15.34180299957396</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>5.166447520771733</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>4.901503528708806</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>6.665865974792577</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>14,16</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1,0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1,0</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>7,0</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>3,09</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>3,09</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>11,89</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>2,75</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>2,4</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>4.778143213406069</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>4.183367588201101</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.7446357323371253</v>
+      </c>
+      <c r="F8" s="5" t="inlineStr"/>
+      <c r="G8" s="5" t="n">
+        <v>1.95490851016897</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>0.2295014082653473</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="J8" s="5" t="inlineStr"/>
+      <c r="K8" s="5" t="n">
+        <v>3.489549646654291</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>2.193076112529371</v>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>2.523161323355021</v>
+      </c>
+      <c r="N8" s="5" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>2,35; 36,0</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>1,5; 5,45</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>1,0; 6,0</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>3,52; 33,42</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>1,42; 5,14</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>1,0; 6,0</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>10.41184644096502</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>20.05793556996144</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>6.059551055356671</v>
+      </c>
+      <c r="F9" s="5" t="inlineStr"/>
+      <c r="G9" s="5" t="n">
+        <v>5.406845633220053</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>1.738655483262564</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="J9" s="5" t="inlineStr"/>
+      <c r="K9" s="5" t="n">
+        <v>8.001497960688171</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>12.18387989688396</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>12.41443773647814</v>
+      </c>
+      <c r="N9" s="5" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1066,137 +869,239 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>5,82</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>10,01</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>6,78</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2,09</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>3,4</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,5</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>6,29</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>3,06</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>4,91</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>7,13</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>6,53</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>2,66</t>
-        </is>
+      <c r="C10" s="5" t="inlineStr"/>
+      <c r="D10" s="5" t="n">
+        <v>14.15786407192333</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="5" t="inlineStr"/>
+      <c r="H10" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>3.094597298638175</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>3.093444219060602</v>
+      </c>
+      <c r="K10" s="5" t="inlineStr"/>
+      <c r="L10" s="5" t="n">
+        <v>11.89461561339403</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>2.745025656820891</v>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>2.399273003498184</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>3,98; 9,02</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>4,57; 20,73</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>1,6; 17,21</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>1,0; 3,0</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>1,95; 5,41</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0,76; 5,84</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>2,76; 12,67</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>1,0; 6,0</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>3,41; 7,05</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>3,69; 15,33</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>3,16; 12,4</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>1,43; 4,55</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr"/>
+      <c r="D11" s="5" t="n">
+        <v>2.35214009879568</v>
+      </c>
+      <c r="E11" s="5" t="inlineStr"/>
+      <c r="F11" s="5" t="inlineStr"/>
+      <c r="G11" s="5" t="inlineStr"/>
+      <c r="H11" s="5" t="inlineStr"/>
+      <c r="I11" s="5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" s="5" t="inlineStr"/>
+      <c r="L11" s="5" t="n">
+        <v>3.521115064067535</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>1.418615838489802</v>
+      </c>
+      <c r="N11" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr"/>
+      <c r="D12" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="E12" s="5" t="inlineStr"/>
+      <c r="F12" s="5" t="inlineStr"/>
+      <c r="G12" s="5" t="inlineStr"/>
+      <c r="H12" s="5" t="inlineStr"/>
+      <c r="I12" s="5" t="n">
+        <v>5.447841973001501</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="K12" s="5" t="inlineStr"/>
+      <c r="L12" s="5" t="n">
+        <v>33.42490768889584</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>5.144915673074445</v>
+      </c>
+      <c r="N12" s="5" t="n">
+        <v>6.000000000000001</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>5.824528216749528</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>10.0117040549995</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>6.783487962433942</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>2.092094372359923</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>3.398623865093191</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>2.495939656690903</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>6.292742909907888</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>3.059347354425384</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>4.908291560630805</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>7.128775094834062</v>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>6.527851752043035</v>
+      </c>
+      <c r="N13" s="5" t="n">
+        <v>2.663058864150678</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>3.977352589402717</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>4.570030226804024</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>1.603195711487401</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>1.95490851016897</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>0.7618187334008142</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>2.756447992739487</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>3.409575231663201</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>3.693502352574127</v>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>3.159197175522068</v>
+      </c>
+      <c r="N14" s="5" t="n">
+        <v>1.433746933250949</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>9.015038195071281</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>20.73114564541212</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>17.20635381634974</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>5.406845633220053</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>5.839270523905964</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>12.67180237597286</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>6.000000000000001</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>7.047702658696782</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>15.33327834137176</v>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>12.39896215667485</v>
+      </c>
+      <c r="N15" s="5" t="n">
+        <v>4.552402015695894</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1204,14 +1109,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
     <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
